--- a/data/trans_dic/P59A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,37</t>
+          <t>6,68; 14,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,91</t>
+          <t>9,5; 18,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 22,13</t>
+          <t>13,01; 22,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,19</t>
+          <t>8,91; 17,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,59</t>
+          <t>3,3; 9,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 17,48</t>
+          <t>8,93; 17,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,61</t>
+          <t>9,73; 17,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 15,37</t>
+          <t>8,82; 15,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,32</t>
+          <t>5,52; 10,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,58</t>
+          <t>9,84; 16,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,15; 18,13</t>
+          <t>12,38; 18,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,3</t>
+          <t>9,63; 15,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 15,94</t>
+          <t>8,28; 15,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 19,75</t>
+          <t>11,85; 19,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,84</t>
+          <t>13,29; 21,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 21,22</t>
+          <t>12,47; 21,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,33</t>
+          <t>6,1; 12,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,82</t>
+          <t>9,52; 16,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 19,62</t>
+          <t>12,32; 19,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 19,51</t>
+          <t>12,59; 19,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,85</t>
+          <t>8,27; 12,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,86</t>
+          <t>11,73; 16,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,74; 18,97</t>
+          <t>13,77; 19,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,51; 19,31</t>
+          <t>13,54; 19,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,69</t>
+          <t>9,53; 19,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 23,42</t>
+          <t>13,99; 23,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,9; 21,63</t>
+          <t>12,96; 21,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,65; 24,75</t>
+          <t>14,42; 25,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,76</t>
+          <t>7,83; 15,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 18,93</t>
+          <t>10,51; 18,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,11</t>
+          <t>10,31; 17,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 21,87</t>
+          <t>13,65; 22,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,56</t>
+          <t>9,72; 16,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 19,66</t>
+          <t>13,13; 19,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 18,22</t>
+          <t>12,66; 18,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 21,88</t>
+          <t>15,13; 21,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 21,31</t>
+          <t>14,29; 21,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 17,82</t>
+          <t>10,83; 17,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 22,84</t>
+          <t>14,95; 22,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,02</t>
+          <t>11,82; 19,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,24</t>
+          <t>10,21; 16,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,09; 20,63</t>
+          <t>13,29; 20,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 16,75</t>
+          <t>11,03; 17,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,49</t>
+          <t>6,61; 12,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 17,54</t>
+          <t>12,95; 17,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,1</t>
+          <t>12,79; 17,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,16</t>
+          <t>13,67; 18,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,45</t>
+          <t>9,52; 14,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,88</t>
+          <t>11,83; 15,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,77</t>
+          <t>13,4; 17,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,57</t>
+          <t>15,53; 19,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,11</t>
+          <t>13,73; 18,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,87</t>
+          <t>8,57; 12,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 16,12</t>
+          <t>12,4; 16,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,92</t>
+          <t>12,37; 16,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,93</t>
+          <t>11,15; 14,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,19</t>
+          <t>10,65; 13,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 16,13</t>
+          <t>13,39; 16,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,06</t>
+          <t>14,45; 17,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 16,07</t>
+          <t>13,01; 15,87</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16634; 37350</t>
+          <t>17367; 37159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26233; 51601</t>
+          <t>25919; 51540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37712; 63394</t>
+          <t>37286; 63395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30506; 62433</t>
+          <t>30572; 61242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9383; 24887</t>
+          <t>8553; 24764</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21016; 44209</t>
+          <t>22574; 45391</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27253; 48911</t>
+          <t>27027; 48843</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28205; 49109</t>
+          <t>28184; 49579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29345; 53620</t>
+          <t>28672; 53996</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53202; 87182</t>
+          <t>51756; 86257</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68561; 102304</t>
+          <t>69882; 104543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64238; 101429</t>
+          <t>63802; 100228</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31017; 57831</t>
+          <t>30046; 57225</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47811; 79001</t>
+          <t>47388; 78902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56980; 91854</t>
+          <t>58563; 92867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57683; 99436</t>
+          <t>58449; 101732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20561; 43506</t>
+          <t>21538; 44325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37268; 65614</t>
+          <t>37130; 64958</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48954; 78230</t>
+          <t>49137; 79135</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54668; 85215</t>
+          <t>55008; 86559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57935; 91976</t>
+          <t>59167; 92966</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91585; 133212</t>
+          <t>92652; 133244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115347; 159227</t>
+          <t>115632; 162081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122288; 174848</t>
+          <t>122578; 172769</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23738; 46288</t>
+          <t>22398; 44881</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43390; 72218</t>
+          <t>43139; 72275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41479; 69563</t>
+          <t>41679; 68830</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50793; 85856</t>
+          <t>50023; 88353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20683; 41960</t>
+          <t>20848; 40436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31406; 57001</t>
+          <t>31655; 56858</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36120; 60801</t>
+          <t>36655; 63194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45946; 74896</t>
+          <t>46742; 76058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46342; 77998</t>
+          <t>48716; 80356</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79856; 119817</t>
+          <t>80047; 118353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84181; 123367</t>
+          <t>85731; 124814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>103398; 150806</t>
+          <t>104266; 150683</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60531; 91720</t>
+          <t>61522; 93214</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43074; 71652</t>
+          <t>43545; 70315</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62032; 94371</t>
+          <t>61758; 94750</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56120; 89587</t>
+          <t>55673; 90547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50438; 81797</t>
+          <t>51426; 83531</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62800; 98936</t>
+          <t>63765; 98303</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60760; 94011</t>
+          <t>61892; 96028</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42642; 81604</t>
+          <t>43193; 81550</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120878; 163826</t>
+          <t>120984; 162922</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114298; 159613</t>
+          <t>112786; 157941</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130377; 176922</t>
+          <t>133178; 178293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107384; 162492</t>
+          <t>106981; 159858</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151556; 204574</t>
+          <t>152374; 203455</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>187924; 245821</t>
+          <t>185313; 241494</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227296; 286069</t>
+          <t>227067; 287809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224744; 295040</t>
+          <t>223772; 297705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118904; 164076</t>
+          <t>118514; 167653</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>177179; 229468</t>
+          <t>176522; 230592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>197988; 253637</t>
+          <t>197057; 255272</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>193613; 261573</t>
+          <t>195437; 260487</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>281649; 352236</t>
+          <t>284463; 353780</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>374364; 452819</t>
+          <t>375886; 456788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>438777; 521238</t>
+          <t>441393; 522749</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>440373; 543579</t>
+          <t>439869; 536616</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P59A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 14,29</t>
+          <t>6,23; 13,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 18,89</t>
+          <t>9,93; 19,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 22,13</t>
+          <t>13,04; 22,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 17,85</t>
+          <t>9,12; 18,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,55</t>
+          <t>3,45; 9,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 17,95</t>
+          <t>8,32; 17,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 17,58</t>
+          <t>9,53; 17,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 15,52</t>
+          <t>8,87; 15,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,4</t>
+          <t>5,61; 10,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,41</t>
+          <t>10,43; 16,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 18,53</t>
+          <t>12,47; 18,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,12</t>
+          <t>10,19; 15,82</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 15,78</t>
+          <t>8,43; 16,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 19,73</t>
+          <t>11,93; 19,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 21,07</t>
+          <t>13,21; 21,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 21,71</t>
+          <t>12,56; 21,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,56</t>
+          <t>6,15; 12,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,65</t>
+          <t>9,58; 17,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 19,85</t>
+          <t>12,28; 19,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 19,82</t>
+          <t>12,33; 18,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,99</t>
+          <t>8,15; 12,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 16,86</t>
+          <t>11,61; 16,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 19,31</t>
+          <t>13,91; 19,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 19,08</t>
+          <t>13,48; 18,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,09</t>
+          <t>9,63; 19,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,99; 23,43</t>
+          <t>14,14; 24,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 21,41</t>
+          <t>12,82; 21,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 25,47</t>
+          <t>14,87; 25,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,19</t>
+          <t>7,64; 15,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 18,88</t>
+          <t>10,69; 19,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,78</t>
+          <t>10,49; 17,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 22,21</t>
+          <t>13,5; 20,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 16,03</t>
+          <t>9,61; 15,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 19,42</t>
+          <t>13,32; 19,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,44</t>
+          <t>12,5; 18,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 21,86</t>
+          <t>15,36; 21,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 21,65</t>
+          <t>13,96; 21,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,49</t>
+          <t>10,87; 17,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,94</t>
+          <t>15,02; 22,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,23</t>
+          <t>11,87; 19,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,58</t>
+          <t>10,1; 16,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 20,49</t>
+          <t>13,33; 20,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 17,11</t>
+          <t>10,65; 16,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,48</t>
+          <t>9,17; 14,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,44</t>
+          <t>13,13; 17,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,91</t>
+          <t>12,91; 17,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 18,3</t>
+          <t>13,49; 18,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 14,22</t>
+          <t>11,18; 15,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,79</t>
+          <t>11,82; 15,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,4; 17,46</t>
+          <t>13,31; 17,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,53; 19,69</t>
+          <t>15,46; 19,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,73; 18,27</t>
+          <t>14,24; 18,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,13</t>
+          <t>8,62; 12,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,2</t>
+          <t>12,24; 16,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,02</t>
+          <t>12,32; 15,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,87</t>
+          <t>12,21; 15,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 13,25</t>
+          <t>10,65; 13,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,39; 16,27</t>
+          <t>13,31; 16,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,11</t>
+          <t>14,38; 17,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,01; 15,87</t>
+          <t>13,8; 16,44</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81018</t>
+          <t>89390</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17367; 37159</t>
+          <t>16198; 35793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25919; 51540</t>
+          <t>27086; 52380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37286; 63395</t>
+          <t>37363; 64659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30572; 61242</t>
+          <t>32886; 65237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8553; 24764</t>
+          <t>8951; 24633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22574; 45391</t>
+          <t>21030; 44121</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27027; 48843</t>
+          <t>26488; 48942</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28184; 49579</t>
+          <t>30759; 55396</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28672; 53996</t>
+          <t>29153; 55320</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51756; 86257</t>
+          <t>54835; 85915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69882; 104543</t>
+          <t>70362; 104443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63802; 100228</t>
+          <t>72096; 111965</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>84886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>75878</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>145672</t>
+          <t>160764</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30046; 57225</t>
+          <t>30572; 58105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47388; 78902</t>
+          <t>47735; 77469</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58563; 92867</t>
+          <t>58214; 92777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58449; 101732</t>
+          <t>63706; 107376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21538; 44325</t>
+          <t>21688; 44239</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37130; 64958</t>
+          <t>37390; 66376</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49137; 79135</t>
+          <t>48967; 79103</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55008; 86559</t>
+          <t>60770; 93422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59167; 92966</t>
+          <t>58322; 92988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92652; 133244</t>
+          <t>91733; 132104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115632; 162081</t>
+          <t>116787; 162342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122578; 172769</t>
+          <t>134768; 188130</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>74518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>126314</t>
+          <t>142380</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22398; 44881</t>
+          <t>22637; 46613</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43139; 72275</t>
+          <t>43606; 74034</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41679; 68830</t>
+          <t>41211; 70093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50023; 88353</t>
+          <t>56886; 97296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20848; 40436</t>
+          <t>20326; 40894</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31655; 56858</t>
+          <t>32177; 57875</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36655; 63194</t>
+          <t>37276; 62910</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46742; 76058</t>
+          <t>53818; 82997</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48716; 80356</t>
+          <t>48193; 78588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80047; 118353</t>
+          <t>81185; 121344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85731; 124814</t>
+          <t>84632; 122057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>104266; 150683</t>
+          <t>119995; 170144</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63629</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>134500</t>
+          <t>150351</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61522; 93214</t>
+          <t>60104; 92815</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43545; 70315</t>
+          <t>43721; 70700</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61758; 94750</t>
+          <t>62040; 92510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55673; 90547</t>
+          <t>59186; 96810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51426; 83531</t>
+          <t>50892; 82101</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63765; 98303</t>
+          <t>63949; 98157</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61892; 96028</t>
+          <t>59771; 93117</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43193; 81550</t>
+          <t>57998; 89483</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120984; 162922</t>
+          <t>122666; 166206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112786; 157941</t>
+          <t>113874; 158142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>133178; 178293</t>
+          <t>131485; 178654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106981; 159858</t>
+          <t>126482; 173941</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>152374; 203455</t>
+          <t>152328; 203813</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185313; 241494</t>
+          <t>184121; 238355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227067; 287809</t>
+          <t>226086; 284564</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>223772; 297705</t>
+          <t>249020; 325349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118514; 167653</t>
+          <t>119166; 166694</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>176522; 230592</t>
+          <t>174290; 233501</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>197057; 255272</t>
+          <t>196240; 254437</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>195437; 260487</t>
+          <t>228445; 283176</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>284463; 353780</t>
+          <t>284529; 357341</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>375886; 456788</t>
+          <t>373746; 452634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>441393; 522749</t>
+          <t>439242; 521488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>439869; 536616</t>
+          <t>499586; 595084</t>
         </is>
       </c>
     </row>
